--- a/artfynd/A 17640-2024 artfynd.xlsx
+++ b/artfynd/A 17640-2024 artfynd.xlsx
@@ -1033,7 +1033,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117753503</v>
+        <v>117753504</v>
       </c>
       <c r="B5" t="n">
         <v>90517</v>
@@ -1073,10 +1073,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>410054</v>
+        <v>410286</v>
       </c>
       <c r="R5" t="n">
-        <v>7064276</v>
+        <v>7063972</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1237,10 +1237,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117753495</v>
+        <v>117753503</v>
       </c>
       <c r="B7" t="n">
-        <v>57287</v>
+        <v>90517</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1253,21 +1253,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1277,10 +1277,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>410130</v>
+        <v>410054</v>
       </c>
       <c r="R7" t="n">
-        <v>7064355</v>
+        <v>7064276</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1313,11 +1313,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-06-13</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1344,7 +1339,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117753494</v>
+        <v>117753496</v>
       </c>
       <c r="B8" t="n">
         <v>57287</v>
@@ -1384,10 +1379,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>410373</v>
+        <v>410005</v>
       </c>
       <c r="R8" t="n">
-        <v>7063984</v>
+        <v>7064421</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,7 +1419,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1451,10 +1446,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117753504</v>
+        <v>117753501</v>
       </c>
       <c r="B9" t="n">
-        <v>90517</v>
+        <v>90495</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1467,21 +1462,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1491,10 +1486,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>410286</v>
+        <v>410061</v>
       </c>
       <c r="R9" t="n">
-        <v>7063972</v>
+        <v>7064249</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1553,10 +1548,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117753501</v>
+        <v>117753505</v>
       </c>
       <c r="B10" t="n">
-        <v>90495</v>
+        <v>90517</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1569,21 +1564,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1593,10 +1588,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>410061</v>
+        <v>410186</v>
       </c>
       <c r="R10" t="n">
-        <v>7064249</v>
+        <v>7064335</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1655,7 +1650,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117753496</v>
+        <v>117753494</v>
       </c>
       <c r="B11" t="n">
         <v>57287</v>
@@ -1695,10 +1690,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>410005</v>
+        <v>410373</v>
       </c>
       <c r="R11" t="n">
-        <v>7064421</v>
+        <v>7063984</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,7 +1730,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1762,10 +1757,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117753505</v>
+        <v>117753495</v>
       </c>
       <c r="B12" t="n">
-        <v>90517</v>
+        <v>57287</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1778,21 +1773,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1802,10 +1797,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>410186</v>
+        <v>410130</v>
       </c>
       <c r="R12" t="n">
-        <v>7064335</v>
+        <v>7064355</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1838,6 +1833,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-06-13</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 17640-2024 artfynd.xlsx
+++ b/artfynd/A 17640-2024 artfynd.xlsx
@@ -1033,10 +1033,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117753504</v>
+        <v>117753501</v>
       </c>
       <c r="B5" t="n">
-        <v>90517</v>
+        <v>90497</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1049,21 +1049,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1073,10 +1073,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>410286</v>
+        <v>410061</v>
       </c>
       <c r="R5" t="n">
-        <v>7063972</v>
+        <v>7064249</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1135,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117753502</v>
+        <v>117753505</v>
       </c>
       <c r="B6" t="n">
-        <v>90495</v>
+        <v>90519</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,21 +1151,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>410143</v>
+        <v>410186</v>
       </c>
       <c r="R6" t="n">
-        <v>7064117</v>
+        <v>7064335</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1237,10 +1237,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117753503</v>
+        <v>117753496</v>
       </c>
       <c r="B7" t="n">
-        <v>90517</v>
+        <v>57288</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1253,21 +1253,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1277,10 +1277,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>410054</v>
+        <v>410005</v>
       </c>
       <c r="R7" t="n">
-        <v>7064276</v>
+        <v>7064421</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1313,6 +1313,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-06-13</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1339,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117753496</v>
+        <v>117753494</v>
       </c>
       <c r="B8" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1379,10 +1384,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>410005</v>
+        <v>410373</v>
       </c>
       <c r="R8" t="n">
-        <v>7064421</v>
+        <v>7063984</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,7 +1424,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1446,10 +1451,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117753501</v>
+        <v>117753502</v>
       </c>
       <c r="B9" t="n">
-        <v>90495</v>
+        <v>90497</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1486,10 +1491,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>410061</v>
+        <v>410143</v>
       </c>
       <c r="R9" t="n">
-        <v>7064249</v>
+        <v>7064117</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1548,10 +1553,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117753505</v>
+        <v>117753495</v>
       </c>
       <c r="B10" t="n">
-        <v>90517</v>
+        <v>57288</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1564,21 +1569,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1588,10 +1593,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>410186</v>
+        <v>410130</v>
       </c>
       <c r="R10" t="n">
-        <v>7064335</v>
+        <v>7064355</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1624,6 +1629,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-06-13</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1650,10 +1660,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117753494</v>
+        <v>117753504</v>
       </c>
       <c r="B11" t="n">
-        <v>57287</v>
+        <v>90519</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1666,21 +1676,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1690,10 +1700,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>410373</v>
+        <v>410286</v>
       </c>
       <c r="R11" t="n">
-        <v>7063984</v>
+        <v>7063972</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1726,11 +1736,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-06-13</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1757,10 +1762,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117753495</v>
+        <v>117753503</v>
       </c>
       <c r="B12" t="n">
-        <v>57287</v>
+        <v>90519</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1773,21 +1778,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1797,10 +1802,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>410130</v>
+        <v>410054</v>
       </c>
       <c r="R12" t="n">
-        <v>7064355</v>
+        <v>7064276</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1833,11 +1838,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-06-13</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
